--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/CONNECTICUT_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/CONNECTICUT_2021.xlsx
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C119">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C347">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C360">
